--- a/payment_forms/036_digital_payment_integration_request_form--payment_forms.xlsx
+++ b/payment_forms/036_digital_payment_integration_request_form--payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>digital_payment_integration_request_form</t>
+          <t>What is the type of integration you are requesting?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>integration_type</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>integration_type</t>
+          <t>What is the payment method you are using?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>payment_method_description</t>
+          <t>Describe your payment method in more detail.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>payment_gateway_description</t>
+          <t>Describe your payment gateway in more detail.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>merchant_id</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>payment_method</t>
+          <t>What is the merchant ID?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>payment_gateway</t>
+          <t>merchant_key</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>payment_gateway</t>
+          <t>What is the merchant key?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>merchant_id</t>
+          <t>api_key</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>merchant_id</t>
+          <t>What is the API key?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>merchant_key</t>
+          <t>api_secret</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>merchant_key</t>
+          <t>What is the API secret?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>api_key</t>
+          <t>confirm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>api_key</t>
+          <t>Do you confirm your payment method selection?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>api_secret</t>
+          <t>payment_gateway_details</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>api_secret</t>
+          <t>Payment Gateway Details</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>payment_method_description_details</t>
+          <t>payment_method_details</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>payment_method_description_details</t>
+          <t>Payment Method Details</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>payment_gateway_description_details</t>
+          <t>payment_method_details_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>payment_gateway_description_details</t>
+          <t>Is the merchant account already set up?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>payment_gateway_details</t>
+          <t>payment_gateway_details_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>payment_gateway_details</t>
+          <t>If set up, provide more details about the merchant account.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>payment_method_details</t>
+          <t>payment_method_details_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>payment_method_details</t>
+          <t>Are you sure about your payment method selection?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>payment_method_details_3</t>
+          <t>payment_gateway_details_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>payment_method_details_3</t>
+          <t>Is everything correct?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>payment_method_details_2</t>
+          <t>payment_method_details_4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>payment_method_details_2</t>
+          <t>Do you have any further questions or concerns?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>payment_gateway_details_2</t>
+          <t>payment_gateway_details_4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>payment_gateway_details_2</t>
+          <t>Describe the payment gateway you selected.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>payment_gateway_details_3</t>
+          <t>payment_gateway_details_5</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>payment_gateway_details_3</t>
+          <t>Payment Gateway Details 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,159 +929,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>merchant_id</t>
+          <t>payment_gateway_details_6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>merchant_id</t>
+          <t>Payment Gateway Details 6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>merchant_key</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>merchant_key</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>api_key</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>api_key</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>api_secret</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>api_secret</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>payment_method</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>payment_method</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>payment_gateway</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>payment_gateway</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>confirm</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>confirm</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +960,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,68 +988,68 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>integration_type_choices</t>
+          <t>digital_payment_integration_request_form_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'payment_gateway',_'label':_'payment_gateway'}</t>
+          <t>payment_gateway</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'payment_gateway', 'label': 'Payment Gateway'}</t>
+          <t>Payment Gateway</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>integration_type_choices</t>
+          <t>digital_payment_integration_request_form_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'payment_method',_'label':_'payment_method'}</t>
+          <t>api_key</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'payment_method', 'label': 'Payment Method'}</t>
+          <t>API Key</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>integration_type_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'api_key',_'label':_'api_key'}</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'api_key', 'label': 'API Key'}</t>
+          <t>Stripe</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>integration_type_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'api_secret',_'label':_'api_secret'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'api_secret', 'label': 'API Secret'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1199,267 +1061,46 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'stripe',_'label':_'stripe'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'stripe', 'label': 'Stripe'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>confirm_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'paypal',_'label':_'paypal'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'paypal', 'label': 'PayPal'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>confirm_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'bank_transfer',_'label':_'bank_transfer'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'bank_transfer', 'label': 'Bank Transfer'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'name':_'google_pay',_'label':_'google_pay'}</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'name': 'google_pay', 'label': 'Google Pay'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'stripe',_'label':_'stripe'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'stripe', 'label': 'Stripe'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'google_pay',_'label':_'google_pay'}</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'google_pay', 'label': 'Google Pay'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'paypal',_'label':_'paypal'}</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'paypal', 'label': 'PayPal'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'stripe',_'label':_'stripe'}</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'stripe', 'label': 'Stripe'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'paypal',_'label':_'paypal'}</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'paypal', 'label': 'PayPal'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'bank_transfer',_'label':_'bank_transfer'}</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'bank_transfer', 'label': 'Bank Transfer'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'name':_'google_pay',_'label':_'google_pay'}</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'name': 'google_pay', 'label': 'Google Pay'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_'stripe',_'label':_'stripe'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': 'stripe', 'label': 'Stripe'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_'google_pay',_'label':_'google_pay'}</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': 'google_pay', 'label': 'Google Pay'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>payment_gateway_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'name':_'paypal',_'label':_'paypal'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'name': 'paypal', 'label': 'PayPal'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>confirm_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'name':_true,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'name': True, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>confirm_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'name':_false,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'name': False, 'label': False}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
